--- a/outputs/57262.xlsx
+++ b/outputs/57262.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,139 +29,263 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material req. (ml)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material cost per 1ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material Cost Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy cost per hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Required
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Item 1</t>
+  </si>
+  <si>
+    <t>Item 2</t>
+  </si>
+  <si>
+    <t>Item 3</t>
+  </si>
+  <si>
+    <t>Item 4</t>
+  </si>
+  <si>
+    <t>Item 5</t>
+  </si>
+  <si>
+    <t>Item 6</t>
+  </si>
+  <si>
+    <t>Item 7</t>
+  </si>
+  <si>
+    <t>Material req. (ml)</t>
+  </si>
+  <si>
+    <t>Material cost per 1ml</t>
+  </si>
+  <si>
+    <t>Material Cost Total</t>
+  </si>
+  <si>
+    <t>Energy cost per hour</t>
+  </si>
+  <si>
+    <t>Time Required
 (r-up to hour)</t>
   </si>
   <si>
-    <t xml:space="preserve">Energy Cost 
+    <t>Energy Cost 
 Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final price point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order 9</t>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Postage</t>
+  </si>
+  <si>
+    <t>final price point</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Order 1</t>
+  </si>
+  <si>
+    <t>Order 2</t>
+  </si>
+  <si>
+    <t>Order 3</t>
+  </si>
+  <si>
+    <t>Order 4</t>
+  </si>
+  <si>
+    <t>Order 5</t>
+  </si>
+  <si>
+    <t>Order 6</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>Order 7</t>
+  </si>
+  <si>
+    <t>Order 8</t>
+  </si>
+  <si>
+    <t>Order 9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* \-??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,202 +294,571 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF46BDC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC5E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46BDC6"/>
-        <bgColor rgb="FF339966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999"/>
-        <bgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="11">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="22" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Good" xfId="20"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF006100"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC5E0B4"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF46BDC6"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -393,55 +893,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -449,24 +1013,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -479,7 +1052,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -489,13 +1068,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -503,6 +1084,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -510,27 +1092,26 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D5:Y25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="5:11">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -539,7 +1120,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="50" spans="4:21">
       <c r="D6" s="2" t="s">
         <v>0</v>
       </c>
@@ -595,60 +1176,59 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="4:21">
       <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="3">
         <v>1</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="4">
         <v>37.46</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="6">
         <v>0.04</v>
       </c>
-      <c r="N7" s="6" t="n">
-        <f aca="false">L7*M7</f>
+      <c r="N7" s="7">
+        <f>L7*M7</f>
         <v>1.4984</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="O7" s="6">
         <v>0.02</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="4">
         <v>8</v>
       </c>
-      <c r="Q7" s="7" t="n">
-        <f aca="false">O7*P7</f>
+      <c r="Q7" s="8">
+        <f>O7*P7</f>
         <v>0.16</v>
       </c>
-      <c r="R7" s="7" t="n">
-        <f aca="false">Q7+N7</f>
+      <c r="R7" s="8">
+        <f>Q7+N7</f>
         <v>1.6584</v>
       </c>
-      <c r="S7" s="5" t="n">
+      <c r="S7" s="6">
         <v>2.9</v>
       </c>
-      <c r="T7" s="5" t="n">
-        <f aca="false">E7*8+F7*8+G7*10+H7*10+I7*12+J7*16+K7*20</f>
+      <c r="T7" s="6">
         <v>10</v>
       </c>
-      <c r="U7" s="5" t="n">
-        <f aca="false">T7-S7-R7</f>
+      <c r="U7" s="6">
+        <f>T7-S7-R7</f>
         <v>5.4416</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="4:21">
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
       <c r="F8" s="4"/>
@@ -657,43 +1237,42 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4">
         <v>14.52</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="6">
         <v>0.04</v>
       </c>
-      <c r="N8" s="6" t="n">
-        <f aca="false">L8*M8</f>
+      <c r="N8" s="7">
+        <f t="shared" ref="N8:N25" si="0">L8*M8</f>
         <v>0.5808</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="O8" s="6">
         <v>0.02</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="4">
         <v>3.25</v>
       </c>
-      <c r="Q8" s="7" t="n">
-        <f aca="false">O8*P8</f>
+      <c r="Q8" s="8">
+        <f t="shared" ref="Q8:Q25" si="1">O8*P8</f>
         <v>0.065</v>
       </c>
-      <c r="R8" s="7" t="n">
-        <f aca="false">Q8+N8</f>
+      <c r="R8" s="8">
+        <f t="shared" ref="R8:R25" si="2">Q8+N8</f>
         <v>0.6458</v>
       </c>
-      <c r="S8" s="5" t="n">
+      <c r="S8" s="6">
         <v>2.9</v>
       </c>
-      <c r="T8" s="5" t="n">
-        <f aca="false">E8*8+F8*8+G8*10+H8*10+I8*12+J8*16+K8*20</f>
+      <c r="T8" s="6">
         <v>8</v>
       </c>
-      <c r="U8" s="5" t="n">
-        <f aca="false">T8-S8-R8</f>
+      <c r="U8" s="6">
+        <f t="shared" ref="U8:U25" si="3">T8-S8-R8</f>
         <v>4.4542</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="4:21">
       <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
@@ -702,96 +1281,94 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="4">
         <v>1</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="4">
         <v>65.26</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="6">
         <v>0.04</v>
       </c>
-      <c r="N9" s="6" t="n">
-        <f aca="false">L9*M9</f>
+      <c r="N9" s="7">
+        <f t="shared" si="0"/>
         <v>2.6104</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="O9" s="6">
         <v>0.02</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="4">
         <v>12.75</v>
       </c>
-      <c r="Q9" s="7" t="n">
-        <f aca="false">O9*P9</f>
+      <c r="Q9" s="8">
+        <f t="shared" si="1"/>
         <v>0.255</v>
       </c>
-      <c r="R9" s="7" t="n">
-        <f aca="false">Q9+N9</f>
+      <c r="R9" s="8">
+        <f t="shared" si="2"/>
         <v>2.8654</v>
       </c>
-      <c r="S9" s="5" t="n">
+      <c r="S9" s="6">
         <v>2.9</v>
       </c>
-      <c r="T9" s="5" t="n">
-        <f aca="false">E9*8+F9*8+G9*10+H9*10+I9*12+J9*16+K9*20</f>
+      <c r="T9" s="6">
         <v>16</v>
       </c>
-      <c r="U9" s="5" t="n">
-        <f aca="false">T9-S9-R9</f>
+      <c r="U9" s="6">
+        <f t="shared" si="3"/>
         <v>10.2346</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="4:21">
       <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>1</v>
       </c>
-      <c r="G10" s="8"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="4">
         <v>4.91</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="6">
         <v>0.04</v>
       </c>
-      <c r="N10" s="6" t="n">
-        <f aca="false">L10*M10</f>
+      <c r="N10" s="7">
+        <f t="shared" si="0"/>
         <v>0.1964</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="O10" s="6">
         <v>0.02</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="4">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="7" t="n">
-        <f aca="false">O10*P10</f>
+      <c r="Q10" s="8">
+        <f t="shared" si="1"/>
         <v>0.052</v>
       </c>
-      <c r="R10" s="7" t="n">
-        <f aca="false">Q10+N10</f>
+      <c r="R10" s="8">
+        <f t="shared" si="2"/>
         <v>0.2484</v>
       </c>
-      <c r="S10" s="5" t="n">
+      <c r="S10" s="6">
         <v>2.9</v>
       </c>
-      <c r="T10" s="5" t="n">
-        <f aca="false">E10*8+F10*8+G10*10+H10*10+I10*12+J10*16+K10*20</f>
+      <c r="T10" s="6">
         <v>8</v>
       </c>
-      <c r="U10" s="5" t="n">
-        <f aca="false">T10-S10-R10</f>
+      <c r="U10" s="6">
+        <f t="shared" si="3"/>
         <v>4.8516</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="4:21">
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
@@ -800,157 +1377,148 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="4">
         <v>56.44</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="6">
         <v>0.04</v>
       </c>
-      <c r="N11" s="6" t="n">
-        <f aca="false">L11*M11</f>
+      <c r="N11" s="7">
+        <f t="shared" si="0"/>
         <v>2.2576</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="O11" s="6">
         <v>0.02</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="4">
         <v>15.75</v>
       </c>
-      <c r="Q11" s="7" t="n">
-        <f aca="false">O11*P11</f>
+      <c r="Q11" s="8">
+        <f t="shared" si="1"/>
         <v>0.315</v>
       </c>
-      <c r="R11" s="7" t="n">
-        <f aca="false">Q11+N11</f>
+      <c r="R11" s="8">
+        <f t="shared" si="2"/>
         <v>2.5726</v>
       </c>
-      <c r="S11" s="5" t="n">
+      <c r="S11" s="6">
         <v>2.9</v>
       </c>
-      <c r="T11" s="5" t="n">
-        <f aca="false">E11*8+F11*8+G11*10+H11*10+I11*12+J11*16+K11*20</f>
-        <v>16</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <f aca="false">T11-S11-R11</f>
-        <v>10.5274</v>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6">
+        <f t="shared" si="3"/>
+        <v>-5.4726</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="4:25">
       <c r="D12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>1</v>
       </c>
-      <c r="G12" s="8"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="4">
         <v>11.33</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="M12" s="6">
         <v>0.04</v>
       </c>
-      <c r="N12" s="6" t="n">
-        <f aca="false">L12*M12</f>
+      <c r="N12" s="7">
+        <f t="shared" si="0"/>
         <v>0.4532</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="O12" s="6">
         <v>0.02</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="4">
         <v>6.5</v>
       </c>
-      <c r="Q12" s="7" t="n">
-        <f aca="false">O12*P12</f>
+      <c r="Q12" s="8">
+        <f t="shared" si="1"/>
         <v>0.13</v>
       </c>
-      <c r="R12" s="7" t="n">
-        <f aca="false">Q12+N12</f>
+      <c r="R12" s="8">
+        <f t="shared" si="2"/>
         <v>0.5832</v>
       </c>
-      <c r="S12" s="5" t="n">
+      <c r="S12" s="6">
         <v>2.9</v>
       </c>
-      <c r="T12" s="5" t="n">
-        <f aca="false">E12*8+F12*8+G12*10+H12*10+I12*12+J12*16+K12*20</f>
-        <v>20</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <f aca="false">T12-S12-R12</f>
-        <v>16.5168</v>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6">
+        <f t="shared" si="3"/>
+        <v>-3.4832</v>
       </c>
       <c r="X12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="Y12" s="9"/>
     </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="4:25">
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="4">
         <v>8.47</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M13" s="6">
         <v>0.04</v>
       </c>
-      <c r="N13" s="6" t="n">
-        <f aca="false">L13*M13</f>
+      <c r="N13" s="7">
+        <f t="shared" si="0"/>
         <v>0.3388</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="O13" s="6">
         <v>0.02</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="4">
         <v>5</v>
       </c>
-      <c r="Q13" s="7" t="n">
-        <f aca="false">O13*P13</f>
+      <c r="Q13" s="8">
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="R13" s="7" t="n">
-        <f aca="false">Q13+N13</f>
+      <c r="R13" s="8">
+        <f t="shared" si="2"/>
         <v>0.4388</v>
       </c>
-      <c r="S13" s="5" t="n">
+      <c r="S13" s="6">
         <v>2.9</v>
       </c>
-      <c r="T13" s="5" t="n">
-        <f aca="false">E13*8+F13*8+G13*10+H13*10+I13*12+J13*16+K13*20</f>
-        <v>8</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <f aca="false">T13-S13-R13</f>
-        <v>4.6612</v>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6">
+        <f t="shared" si="3"/>
+        <v>-3.3388</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Y13" s="5" t="n">
+      <c r="Y13" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="4:25">
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
@@ -958,109 +1526,103 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="4">
         <v>8.66</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="M14" s="6">
         <v>0.04</v>
       </c>
-      <c r="N14" s="6" t="n">
-        <f aca="false">L14*M14</f>
+      <c r="N14" s="7">
+        <f t="shared" si="0"/>
         <v>0.3464</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O14" s="6">
         <v>0.02</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="4">
         <v>5.3</v>
       </c>
-      <c r="Q14" s="7" t="n">
-        <f aca="false">O14*P14</f>
+      <c r="Q14" s="8">
+        <f t="shared" si="1"/>
         <v>0.106</v>
       </c>
-      <c r="R14" s="7" t="n">
-        <f aca="false">Q14+N14</f>
+      <c r="R14" s="8">
+        <f t="shared" si="2"/>
         <v>0.4524</v>
       </c>
-      <c r="S14" s="5" t="n">
+      <c r="S14" s="6">
         <v>2.9</v>
       </c>
-      <c r="T14" s="5" t="n">
-        <f aca="false">E14*8+F14*8+G14*10+H14*10+I14*12+J14*16+K14*20</f>
-        <v>12</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <f aca="false">T14-S14-R14</f>
-        <v>8.6476</v>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6">
+        <f t="shared" si="3"/>
+        <v>-3.3524</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Y14" s="5" t="n">
+      <c r="Y14" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="4:25">
       <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="4">
         <v>4</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="4">
         <v>30.06</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="M15" s="6">
         <v>0.04</v>
       </c>
-      <c r="N15" s="6" t="n">
-        <f aca="false">L15*M15</f>
+      <c r="N15" s="7">
+        <f t="shared" si="0"/>
         <v>1.2024</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="O15" s="6">
         <v>0.02</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P15" s="4">
         <v>5.3</v>
       </c>
-      <c r="Q15" s="7" t="n">
-        <f aca="false">O15*P15</f>
+      <c r="Q15" s="8">
+        <f t="shared" si="1"/>
         <v>0.106</v>
       </c>
-      <c r="R15" s="7" t="n">
-        <f aca="false">Q15+N15</f>
+      <c r="R15" s="8">
+        <f t="shared" si="2"/>
         <v>1.3084</v>
       </c>
-      <c r="S15" s="5" t="n">
+      <c r="S15" s="6">
         <v>2.9</v>
       </c>
-      <c r="T15" s="5" t="n">
-        <f aca="false">E15*8+F15*8+G15*10+H15*10+I15*12+J15*16+K15*20</f>
-        <v>32</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <f aca="false">T15-S15-R15</f>
-        <v>27.7916</v>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6">
+        <f t="shared" si="3"/>
+        <v>-4.2084</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y15" s="5" t="n">
+      <c r="Y15" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="4:25">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,39 +1632,39 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="5" t="n">
+      <c r="M16" s="6">
         <v>0.04</v>
       </c>
-      <c r="N16" s="6" t="n">
-        <f aca="false">L16*M16</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
+      <c r="N16" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
         <v>0.02</v>
       </c>
       <c r="P16" s="3"/>
-      <c r="Q16" s="7" t="n">
-        <f aca="false">O16*P16</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <f aca="false">Q16+N16</f>
+      <c r="Q16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
-      <c r="U16" s="5" t="n">
-        <f aca="false">T16-S16-R16</f>
+      <c r="U16" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y16" s="5" t="n">
+      <c r="Y16" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="4:25">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1112,39 +1674,39 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="5" t="n">
+      <c r="M17" s="6">
         <v>0.04</v>
       </c>
-      <c r="N17" s="6" t="n">
-        <f aca="false">L17*M17</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="n">
+      <c r="N17" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
         <v>0.02</v>
       </c>
       <c r="P17" s="3"/>
-      <c r="Q17" s="7" t="n">
-        <f aca="false">O17*P17</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="n">
-        <f aca="false">Q17+N17</f>
+      <c r="Q17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
-      <c r="U17" s="5" t="n">
-        <f aca="false">T17-S17-R17</f>
+      <c r="U17" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y17" s="5" t="n">
+      <c r="Y17" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="4:25">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1154,39 +1716,39 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="5" t="n">
+      <c r="M18" s="6">
         <v>0.04</v>
       </c>
-      <c r="N18" s="6" t="n">
-        <f aca="false">L18*M18</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
+      <c r="N18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
         <v>0.02</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="Q18" s="7" t="n">
-        <f aca="false">O18*P18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <f aca="false">Q18+N18</f>
+      <c r="Q18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
-      <c r="U18" s="5" t="n">
-        <f aca="false">T18-S18-R18</f>
+      <c r="U18" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Y18" s="5" t="n">
+      <c r="Y18" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="4:25">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1196,39 +1758,39 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="5" t="n">
+      <c r="M19" s="6">
         <v>0.04</v>
       </c>
-      <c r="N19" s="6" t="n">
-        <f aca="false">L19*M19</f>
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="n">
+      <c r="N19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="6">
         <v>0.02</v>
       </c>
       <c r="P19" s="3"/>
-      <c r="Q19" s="7" t="n">
-        <f aca="false">O19*P19</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <f aca="false">Q19+N19</f>
+      <c r="Q19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
-      <c r="U19" s="5" t="n">
-        <f aca="false">T19-S19-R19</f>
+      <c r="U19" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="Y19" s="5" t="n">
+      <c r="Y19" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="4:21">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1238,33 +1800,33 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="5" t="n">
+      <c r="M20" s="6">
         <v>0.04</v>
       </c>
-      <c r="N20" s="6" t="n">
-        <f aca="false">L20*M20</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
+      <c r="N20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="6">
         <v>0.02</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="7" t="n">
-        <f aca="false">O20*P20</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <f aca="false">Q20+N20</f>
+      <c r="Q20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
-      <c r="U20" s="5" t="n">
-        <f aca="false">T20-S20-R20</f>
+      <c r="U20" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="4:21">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1274,33 +1836,33 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="5" t="n">
+      <c r="M21" s="6">
         <v>0.04</v>
       </c>
-      <c r="N21" s="6" t="n">
-        <f aca="false">L21*M21</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="n">
+      <c r="N21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
         <v>0.02</v>
       </c>
       <c r="P21" s="3"/>
-      <c r="Q21" s="7" t="n">
-        <f aca="false">O21*P21</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <f aca="false">Q21+N21</f>
+      <c r="Q21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-      <c r="U21" s="5" t="n">
-        <f aca="false">T21-S21-R21</f>
+      <c r="U21" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="4:21">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1310,33 +1872,33 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="5" t="n">
+      <c r="M22" s="6">
         <v>0.04</v>
       </c>
-      <c r="N22" s="6" t="n">
-        <f aca="false">L22*M22</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
+      <c r="N22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
         <v>0.02</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="Q22" s="7" t="n">
-        <f aca="false">O22*P22</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="7" t="n">
-        <f aca="false">Q22+N22</f>
+      <c r="Q22" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
-      <c r="U22" s="5" t="n">
-        <f aca="false">T22-S22-R22</f>
+      <c r="U22" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="4:21">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1346,33 +1908,33 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="5" t="n">
+      <c r="M23" s="6">
         <v>0.04</v>
       </c>
-      <c r="N23" s="6" t="n">
-        <f aca="false">L23*M23</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="n">
+      <c r="N23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="6">
         <v>0.02</v>
       </c>
       <c r="P23" s="3"/>
-      <c r="Q23" s="7" t="n">
-        <f aca="false">O23*P23</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="7" t="n">
-        <f aca="false">Q23+N23</f>
+      <c r="Q23" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
-      <c r="U23" s="5" t="n">
-        <f aca="false">T23-S23-R23</f>
+      <c r="U23" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="4:21">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1382,33 +1944,33 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="5" t="n">
+      <c r="M24" s="6">
         <v>0.04</v>
       </c>
-      <c r="N24" s="6" t="n">
-        <f aca="false">L24*M24</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
+      <c r="N24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="6">
         <v>0.02</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="7" t="n">
-        <f aca="false">O24*P24</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <f aca="false">Q24+N24</f>
+      <c r="Q24" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
-      <c r="U24" s="5" t="n">
-        <f aca="false">T24-S24-R24</f>
+      <c r="U24" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="4:21">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1418,29 +1980,29 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="5" t="n">
+      <c r="M25" s="6">
         <v>0.04</v>
       </c>
-      <c r="N25" s="6" t="n">
-        <f aca="false">L25*M25</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="5" t="n">
+      <c r="N25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="6">
         <v>0.02</v>
       </c>
       <c r="P25" s="3"/>
-      <c r="Q25" s="7" t="n">
-        <f aca="false">O25*P25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <f aca="false">Q25+N25</f>
+      <c r="Q25" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
-      <c r="U25" s="5" t="n">
-        <f aca="false">T25-S25-R25</f>
+      <c r="U25" s="6">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1448,12 +2010,8 @@
   <mergeCells count="1">
     <mergeCell ref="X12:Y12"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="77" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="122" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>